--- a/Team-Data/2015-16/4-10-2015-16.xlsx
+++ b/Team-Data/2015-16/4-10-2015-16.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E2" t="n">
         <v>48</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.608</v>
+        <v>0.6</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
@@ -679,10 +746,10 @@
         <v>38.7</v>
       </c>
       <c r="J2" t="n">
-        <v>84.5</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
         <v>10</v>
@@ -691,13 +758,13 @@
         <v>28.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O2" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="P2" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="Q2" t="n">
         <v>0.786</v>
@@ -709,22 +776,22 @@
         <v>33.8</v>
       </c>
       <c r="T2" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U2" t="n">
         <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W2" t="n">
         <v>9.1</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z2" t="n">
         <v>19.1</v>
@@ -733,13 +800,13 @@
         <v>18.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.1</v>
+        <v>103</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE2" t="n">
         <v>7</v>
@@ -751,13 +818,13 @@
         <v>7</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI2" t="n">
         <v>8</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK2" t="n">
         <v>11</v>
@@ -769,10 +836,10 @@
         <v>7</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>30</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>3</v>
@@ -805,16 +872,16 @@
         <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB2" t="n">
         <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F3" t="n">
         <v>33</v>
       </c>
       <c r="G3" t="n">
-        <v>0.582</v>
+        <v>0.588</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
@@ -876,13 +943,13 @@
         <v>0.335</v>
       </c>
       <c r="O3" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P3" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R3" t="n">
         <v>11.6</v>
@@ -894,10 +961,10 @@
         <v>45</v>
       </c>
       <c r="U3" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="V3" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W3" t="n">
         <v>9.199999999999999</v>
@@ -912,16 +979,16 @@
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB3" t="n">
-        <v>105.8</v>
+        <v>105.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>8</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>12</v>
@@ -951,7 +1018,7 @@
         <v>10</v>
       </c>
       <c r="AN3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO3" t="n">
         <v>10</v>
@@ -960,13 +1027,13 @@
         <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AR3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -981,19 +1048,19 @@
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ3" t="n">
         <v>29</v>
       </c>
       <c r="BA3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
         <v>8</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -1049,34 +1116,34 @@
         <v>0.454</v>
       </c>
       <c r="L4" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="M4" t="n">
-        <v>18.3</v>
+        <v>17.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O4" t="n">
         <v>15.7</v>
       </c>
       <c r="P4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0.759</v>
       </c>
       <c r="R4" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S4" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T4" t="n">
-        <v>42.4</v>
+        <v>42.5</v>
       </c>
       <c r="U4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V4" t="n">
         <v>14.9</v>
@@ -1094,22 +1161,22 @@
         <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>-7.2</v>
+        <v>-7.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>28</v>
       </c>
       <c r="AF4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG4" t="n">
         <v>28</v>
@@ -1118,10 +1185,10 @@
         <v>26</v>
       </c>
       <c r="AI4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>13</v>
@@ -1130,7 +1197,7 @@
         <v>26</v>
       </c>
       <c r="AM4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN4" t="n">
         <v>13</v>
@@ -1154,7 +1221,7 @@
         <v>23</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
@@ -1163,7 +1230,7 @@
         <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY4" t="n">
         <v>17</v>
@@ -1175,7 +1242,7 @@
         <v>28</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -1222,31 +1289,31 @@
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L5" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M5" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.362</v>
+        <v>0.361</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.792</v>
+        <v>0.79</v>
       </c>
       <c r="R5" t="n">
         <v>9</v>
@@ -1258,13 +1325,13 @@
         <v>43.9</v>
       </c>
       <c r="U5" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X5" t="n">
         <v>5.4</v>
@@ -1273,7 +1340,7 @@
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA5" t="n">
         <v>20.4</v>
@@ -1282,40 +1349,40 @@
         <v>103.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF5" t="n">
         <v>8</v>
       </c>
       <c r="AG5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH5" t="n">
         <v>8</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>9</v>
       </c>
       <c r="AI5" t="n">
         <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
         <v>27</v>
       </c>
       <c r="AL5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM5" t="n">
         <v>4</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
         <v>7</v>
@@ -1324,16 +1391,16 @@
         <v>11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>4</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU5" t="n">
         <v>19</v>
@@ -1342,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX5" t="n">
         <v>12</v>
@@ -1351,7 +1418,7 @@
         <v>24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA5" t="n">
         <v>14</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" t="n">
         <v>40</v>
       </c>
       <c r="G6" t="n">
-        <v>0.487</v>
+        <v>0.5</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
@@ -1407,10 +1474,10 @@
         <v>38.5</v>
       </c>
       <c r="J6" t="n">
-        <v>87.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
         <v>7.8</v>
@@ -1419,7 +1486,7 @@
         <v>21.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O6" t="n">
         <v>16.4</v>
@@ -1428,19 +1495,19 @@
         <v>20.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="T6" t="n">
         <v>46.4</v>
       </c>
       <c r="U6" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V6" t="n">
         <v>13.9</v>
@@ -1455,31 +1522,31 @@
         <v>5.7</v>
       </c>
       <c r="Z6" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA6" t="n">
         <v>18.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.1</v>
+        <v>101.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>-2</v>
+        <v>-1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>11</v>
@@ -1491,7 +1558,7 @@
         <v>25</v>
       </c>
       <c r="AL6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AM6" t="n">
         <v>24</v>
@@ -1500,16 +1567,16 @@
         <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP6" t="n">
         <v>26</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS6" t="n">
         <v>3</v>
@@ -1518,7 +1585,7 @@
         <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>13</v>
@@ -1530,19 +1597,19 @@
         <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AZ6" t="n">
         <v>5</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
         <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -1571,25 +1638,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" t="n">
-        <v>0.705</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J7" t="n">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K7" t="n">
         <v>0.46</v>
@@ -1604,25 +1671,25 @@
         <v>0.362</v>
       </c>
       <c r="O7" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.749</v>
+        <v>0.746</v>
       </c>
       <c r="R7" t="n">
         <v>10.7</v>
       </c>
       <c r="S7" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="T7" t="n">
-        <v>44.3</v>
+        <v>44.5</v>
       </c>
       <c r="U7" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V7" t="n">
         <v>13.6</v>
@@ -1637,19 +1704,19 @@
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="AA7" t="n">
         <v>20.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>104.3</v>
+        <v>104.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AD7" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>3</v>
@@ -1661,7 +1728,7 @@
         <v>3</v>
       </c>
       <c r="AH7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="n">
         <v>10</v>
@@ -1679,13 +1746,13 @@
         <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ7" t="n">
         <v>21</v>
@@ -1694,28 +1761,28 @@
         <v>12</v>
       </c>
       <c r="AS7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY7" t="n">
         <v>7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -1756,34 +1823,34 @@
         <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>0.506</v>
+        <v>0.519</v>
       </c>
       <c r="H8" t="n">
         <v>48.8</v>
       </c>
       <c r="I8" t="n">
-        <v>37.4</v>
+        <v>37.6</v>
       </c>
       <c r="J8" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>28.5</v>
+        <v>28.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.344</v>
+        <v>0.346</v>
       </c>
       <c r="O8" t="n">
         <v>17.7</v>
@@ -1792,7 +1859,7 @@
         <v>22.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.796</v>
+        <v>0.795</v>
       </c>
       <c r="R8" t="n">
         <v>9.199999999999999</v>
@@ -1807,7 +1874,7 @@
         <v>22.2</v>
       </c>
       <c r="V8" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W8" t="n">
         <v>6.8</v>
@@ -1816,28 +1883,28 @@
         <v>3.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>102.3</v>
+        <v>102.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>15</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>15</v>
@@ -1846,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="AI8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ8" t="n">
         <v>17</v>
@@ -1858,10 +1925,10 @@
         <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AO8" t="n">
         <v>12</v>
@@ -1876,13 +1943,13 @@
         <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV8" t="n">
         <v>2</v>
@@ -1894,7 +1961,7 @@
         <v>29</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>8</v>
@@ -1903,10 +1970,10 @@
         <v>8</v>
       </c>
       <c r="BB8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC8" t="n">
         <v>15</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>16</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -1938,25 +2005,25 @@
         <v>80</v>
       </c>
       <c r="E9" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4</v>
+        <v>0.413</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="J9" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L9" t="n">
         <v>8</v>
@@ -1965,7 +2032,7 @@
         <v>23.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="O9" t="n">
         <v>18.6</v>
@@ -1983,49 +2050,49 @@
         <v>33.1</v>
       </c>
       <c r="T9" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U9" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V9" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W9" t="n">
         <v>7.4</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" t="n">
         <v>6.3</v>
       </c>
       <c r="Z9" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AA9" t="n">
         <v>21</v>
       </c>
-      <c r="AA9" t="n">
-        <v>20.9</v>
-      </c>
       <c r="AB9" t="n">
-        <v>101.9</v>
+        <v>102.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.3</v>
+        <v>-2.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>19</v>
@@ -2034,16 +2101,16 @@
         <v>11</v>
       </c>
       <c r="AK9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO9" t="n">
         <v>9</v>
@@ -2064,10 +2131,10 @@
         <v>8</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
@@ -2082,13 +2149,13 @@
         <v>23</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BC9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E10" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F10" t="n">
         <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.526</v>
+        <v>0.538</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
       </c>
       <c r="I10" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J10" t="n">
         <v>86.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="L10" t="n">
         <v>9</v>
       </c>
       <c r="M10" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O10" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P10" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.664</v>
+        <v>0.666</v>
       </c>
       <c r="R10" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S10" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T10" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="U10" t="n">
         <v>19.4</v>
@@ -2174,7 +2241,7 @@
         <v>13.5</v>
       </c>
       <c r="W10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X10" t="n">
         <v>3.6</v>
@@ -2186,28 +2253,28 @@
         <v>19.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB10" t="n">
         <v>102</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
         <v>18</v>
@@ -2216,7 +2283,7 @@
         <v>5</v>
       </c>
       <c r="AK10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL10" t="n">
         <v>11</v>
@@ -2240,7 +2307,7 @@
         <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>3</v>
@@ -2261,7 +2328,7 @@
         <v>8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -2314,46 +2381,46 @@
         <v>48.5</v>
       </c>
       <c r="I11" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="J11" t="n">
-        <v>87.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.488</v>
+        <v>0.487</v>
       </c>
       <c r="L11" t="n">
         <v>13.1</v>
       </c>
       <c r="M11" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.417</v>
+        <v>0.416</v>
       </c>
       <c r="O11" t="n">
         <v>16.7</v>
       </c>
       <c r="P11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
         <v>36.2</v>
       </c>
       <c r="T11" t="n">
-        <v>46</v>
+        <v>46.1</v>
       </c>
       <c r="U11" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="V11" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W11" t="n">
         <v>8.4</v>
@@ -2362,22 +2429,22 @@
         <v>6.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.7</v>
+        <v>20.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>114.8</v>
+        <v>115.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,7 +2456,7 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2413,13 +2480,13 @@
         <v>22</v>
       </c>
       <c r="AP11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
@@ -2431,7 +2498,7 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW11" t="n">
         <v>9</v>
@@ -2443,7 +2510,7 @@
         <v>3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA11" t="n">
         <v>18</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -2484,40 +2551,40 @@
         <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G12" t="n">
-        <v>0.494</v>
+        <v>0.481</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="J12" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L12" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M12" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
         <v>20.6</v>
       </c>
       <c r="P12" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="Q12" t="n">
         <v>0.695</v>
@@ -2529,58 +2596,58 @@
         <v>31.6</v>
       </c>
       <c r="T12" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V12" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="W12" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="X12" t="n">
         <v>5.2</v>
       </c>
       <c r="Y12" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.4</v>
+        <v>105.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.3</v>
+        <v>-0.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AJ12" t="n">
         <v>23</v>
       </c>
       <c r="AK12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL12" t="n">
         <v>3</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
         <v>3</v>
@@ -2598,7 +2665,7 @@
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AR12" t="n">
         <v>7</v>
@@ -2607,10 +2674,10 @@
         <v>27</v>
       </c>
       <c r="AT12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV12" t="n">
         <v>27</v>
@@ -2619,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
         <v>13</v>
@@ -2631,10 +2698,10 @@
         <v>1</v>
       </c>
       <c r="BB12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -2666,31 +2733,31 @@
         <v>79</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>0.544</v>
+        <v>0.532</v>
       </c>
       <c r="H13" t="n">
         <v>48.5</v>
       </c>
       <c r="I13" t="n">
-        <v>38.4</v>
+        <v>38.2</v>
       </c>
       <c r="J13" t="n">
         <v>85.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L13" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M13" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="N13" t="n">
         <v>0.349</v>
@@ -2699,25 +2766,25 @@
         <v>17.5</v>
       </c>
       <c r="P13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R13" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>33.9</v>
+        <v>33.7</v>
       </c>
       <c r="T13" t="n">
-        <v>44.3</v>
+        <v>44</v>
       </c>
       <c r="U13" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
         <v>9</v>
@@ -2726,43 +2793,43 @@
         <v>4.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA13" t="n">
         <v>20.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>102.3</v>
+        <v>101.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF13" t="n">
         <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
         <v>5</v>
       </c>
       <c r="AI13" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ13" t="n">
         <v>13</v>
       </c>
       <c r="AK13" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AL13" t="n">
         <v>18</v>
@@ -2783,19 +2850,19 @@
         <v>15</v>
       </c>
       <c r="AR13" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
         <v>22</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>4</v>
@@ -2813,10 +2880,10 @@
         <v>13</v>
       </c>
       <c r="BB13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2933,7 @@
         <v>82.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
         <v>9.699999999999999</v>
@@ -2875,7 +2942,7 @@
         <v>26.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.364</v>
+        <v>0.362</v>
       </c>
       <c r="O14" t="n">
         <v>18.3</v>
@@ -2884,7 +2951,7 @@
         <v>26.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="R14" t="n">
         <v>8.9</v>
@@ -2896,34 +2963,34 @@
         <v>42.1</v>
       </c>
       <c r="U14" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V14" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
       </c>
       <c r="X14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Z14" t="n">
         <v>21.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>104.3</v>
+        <v>104.5</v>
       </c>
       <c r="AC14" t="n">
         <v>4.1</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
         <v>6</v>
@@ -2935,10 +3002,10 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ14" t="n">
         <v>25</v>
@@ -2962,13 +3029,13 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>29</v>
       </c>
       <c r="AS14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT14" t="n">
         <v>24</v>
@@ -2998,7 +3065,7 @@
         <v>7</v>
       </c>
       <c r="BC14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -3042,49 +3109,49 @@
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J15" t="n">
-        <v>84.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.415</v>
+        <v>0.414</v>
       </c>
       <c r="L15" t="n">
         <v>7.8</v>
       </c>
       <c r="M15" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.32</v>
+        <v>0.318</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="P15" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.776</v>
+        <v>0.778</v>
       </c>
       <c r="R15" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S15" t="n">
         <v>32.1</v>
       </c>
       <c r="T15" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U15" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="V15" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X15" t="n">
         <v>4.2</v>
@@ -3093,19 +3160,19 @@
         <v>5.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AB15" t="n">
         <v>97.40000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>-9.6</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>29</v>
@@ -3129,7 +3196,7 @@
         <v>30</v>
       </c>
       <c r="AL15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
         <v>13</v>
@@ -3144,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR15" t="n">
         <v>11</v>
@@ -3153,16 +3220,16 @@
         <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AU15" t="n">
         <v>30</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>24</v>
@@ -3171,10 +3238,10 @@
         <v>25</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -3209,43 +3276,43 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E16" t="n">
         <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.532</v>
+        <v>0.525</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J16" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L16" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M16" t="n">
         <v>18.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.335</v>
+        <v>0.332</v>
       </c>
       <c r="O16" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P16" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q16" t="n">
         <v>0.784</v>
@@ -3260,10 +3327,10 @@
         <v>41.7</v>
       </c>
       <c r="U16" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V16" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W16" t="n">
         <v>8.800000000000001</v>
@@ -3275,40 +3342,40 @@
         <v>5.7</v>
       </c>
       <c r="Z16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA16" t="n">
         <v>21.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.4</v>
+        <v>-1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3317,7 +3384,7 @@
         <v>26</v>
       </c>
       <c r="AN16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
         <v>5</v>
@@ -3326,10 +3393,10 @@
         <v>8</v>
       </c>
       <c r="AQ16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR16" t="n">
         <v>8</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>9</v>
       </c>
       <c r="AS16" t="n">
         <v>30</v>
@@ -3350,7 +3417,7 @@
         <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ16" t="n">
         <v>27</v>
@@ -3362,7 +3429,7 @@
         <v>24</v>
       </c>
       <c r="BC16" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3473,7 @@
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J17" t="n">
         <v>81.7</v>
@@ -3415,19 +3482,19 @@
         <v>0.47</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M17" t="n">
         <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="O17" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P17" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q17" t="n">
         <v>0.742</v>
@@ -3442,46 +3509,46 @@
         <v>44.2</v>
       </c>
       <c r="U17" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W17" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="X17" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y17" t="n">
         <v>4.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="AA17" t="n">
         <v>19.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>100.2</v>
+        <v>100</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF17" t="n">
         <v>8</v>
       </c>
       <c r="AG17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI17" t="n">
         <v>13</v>
@@ -3496,22 +3563,22 @@
         <v>28</v>
       </c>
       <c r="AM17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AQ17" t="n">
         <v>24</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
         <v>6</v>
@@ -3526,7 +3593,7 @@
         <v>14</v>
       </c>
       <c r="AW17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX17" t="n">
         <v>1</v>
@@ -3535,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
         <v>20</v>
@@ -3544,7 +3611,7 @@
         <v>23</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -3576,55 +3643,55 @@
         <v>79</v>
       </c>
       <c r="E18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G18" t="n">
-        <v>0.418</v>
+        <v>0.405</v>
       </c>
       <c r="H18" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.4</v>
+        <v>38.3</v>
       </c>
       <c r="J18" t="n">
         <v>82.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.468</v>
+        <v>0.467</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O18" t="n">
         <v>17</v>
       </c>
       <c r="P18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.744</v>
+        <v>0.745</v>
       </c>
       <c r="R18" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S18" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
         <v>41.5</v>
       </c>
       <c r="U18" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V18" t="n">
         <v>15.1</v>
@@ -3639,31 +3706,31 @@
         <v>5.6</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.2</v>
+        <v>99</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.8</v>
+        <v>-4.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF18" t="n">
         <v>21</v>
       </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
         <v>14</v>
@@ -3681,7 +3748,7 @@
         <v>30</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AO18" t="n">
         <v>20</v>
@@ -3705,16 +3772,16 @@
         <v>8</v>
       </c>
       <c r="AV18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
       </c>
       <c r="AY18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
         <v>18</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
         <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>0.342</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
@@ -3785,16 +3852,16 @@
         <v>16.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.338</v>
+        <v>0.337</v>
       </c>
       <c r="O19" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P19" t="n">
-        <v>26.8</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.792</v>
+        <v>0.793</v>
       </c>
       <c r="R19" t="n">
         <v>10.1</v>
@@ -3821,19 +3888,19 @@
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>101.7</v>
+        <v>101.9</v>
       </c>
       <c r="AC19" t="n">
         <v>-3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
@@ -3845,7 +3912,7 @@
         <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI19" t="n">
         <v>21</v>
@@ -3863,31 +3930,31 @@
         <v>29</v>
       </c>
       <c r="AN19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO19" t="n">
         <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS19" t="n">
         <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU19" t="n">
         <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW19" t="n">
         <v>14</v>
@@ -3902,7 +3969,7 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -3937,37 +4004,37 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E20" t="n">
         <v>30</v>
       </c>
       <c r="F20" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>0.385</v>
+        <v>0.375</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L20" t="n">
         <v>8.5</v>
       </c>
       <c r="M20" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.359</v>
+        <v>0.358</v>
       </c>
       <c r="O20" t="n">
         <v>17.2</v>
@@ -3976,22 +4043,22 @@
         <v>22.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R20" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="S20" t="n">
-        <v>33.4</v>
+        <v>33.3</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
         <v>7.7</v>
@@ -4000,34 +4067,34 @@
         <v>4.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z20" t="n">
         <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>102.7</v>
+        <v>102.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3</v>
+        <v>-3.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>25</v>
       </c>
       <c r="AF20" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG20" t="n">
         <v>25</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI20" t="n">
         <v>12</v>
@@ -4036,61 +4103,61 @@
         <v>8</v>
       </c>
       <c r="AK20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN20" t="n">
         <v>10</v>
       </c>
       <c r="AO20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV20" t="n">
         <v>8</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AX20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>15</v>
       </c>
       <c r="AZ20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA20" t="n">
         <v>19</v>
       </c>
       <c r="BB20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -4122,25 +4189,25 @@
         <v>80</v>
       </c>
       <c r="E21" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F21" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G21" t="n">
-        <v>0.388</v>
+        <v>0.4</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
       </c>
       <c r="I21" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J21" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K21" t="n">
-        <v>0.439</v>
+        <v>0.44</v>
       </c>
       <c r="L21" t="n">
         <v>7.4</v>
@@ -4149,19 +4216,19 @@
         <v>21.4</v>
       </c>
       <c r="N21" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O21" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q21" t="n">
         <v>0.804</v>
       </c>
       <c r="R21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S21" t="n">
         <v>34.1</v>
@@ -4170,55 +4237,55 @@
         <v>44.4</v>
       </c>
       <c r="U21" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V21" t="n">
         <v>13.4</v>
       </c>
       <c r="W21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X21" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y21" t="n">
         <v>4.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK21" t="n">
         <v>24</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>25</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>26</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>24</v>
@@ -4227,16 +4294,16 @@
         <v>23</v>
       </c>
       <c r="AN21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP21" t="n">
         <v>25</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>17</v>
@@ -4245,7 +4312,7 @@
         <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU21" t="n">
         <v>26</v>
@@ -4263,13 +4330,13 @@
         <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F22" t="n">
         <v>26</v>
       </c>
       <c r="G22" t="n">
-        <v>0.671</v>
+        <v>0.675</v>
       </c>
       <c r="H22" t="n">
         <v>48.3</v>
@@ -4322,16 +4389,16 @@
         <v>86.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.477</v>
+        <v>0.478</v>
       </c>
       <c r="L22" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O22" t="n">
         <v>19.7</v>
@@ -4340,16 +4407,16 @@
         <v>25.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.781</v>
+        <v>0.783</v>
       </c>
       <c r="R22" t="n">
         <v>13</v>
       </c>
       <c r="S22" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="T22" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="U22" t="n">
         <v>23</v>
@@ -4364,22 +4431,22 @@
         <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z22" t="n">
         <v>20.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>110.3</v>
+        <v>110.4</v>
       </c>
       <c r="AC22" t="n">
         <v>7.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>4</v>
@@ -4397,7 +4464,7 @@
         <v>2</v>
       </c>
       <c r="AJ22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
         <v>3</v>
@@ -4439,7 +4506,7 @@
         <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -4501,19 +4568,19 @@
         <v>39.5</v>
       </c>
       <c r="J23" t="n">
-        <v>86.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L23" t="n">
         <v>7.8</v>
       </c>
       <c r="M23" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="N23" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O23" t="n">
         <v>15.3</v>
@@ -4522,16 +4589,16 @@
         <v>20.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.762</v>
+        <v>0.761</v>
       </c>
       <c r="R23" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="S23" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.6</v>
       </c>
       <c r="U23" t="n">
         <v>23.6</v>
@@ -4543,25 +4610,25 @@
         <v>8.1</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA23" t="n">
         <v>18.3</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.2</v>
+        <v>102.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>-1.6</v>
+        <v>-1.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
@@ -4573,7 +4640,7 @@
         <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>5</v>
@@ -4591,7 +4658,7 @@
         <v>22</v>
       </c>
       <c r="AN23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO23" t="n">
         <v>30</v>
@@ -4600,16 +4667,16 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR23" t="n">
         <v>16</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>18</v>
       </c>
       <c r="AS23" t="n">
         <v>19</v>
       </c>
       <c r="AT23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AU23" t="n">
         <v>7</v>
@@ -4624,10 +4691,10 @@
         <v>15</v>
       </c>
       <c r="AY23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>21</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>20</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
@@ -4636,7 +4703,7 @@
         <v>17</v>
       </c>
       <c r="BC23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -4680,22 +4747,22 @@
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J24" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K24" t="n">
         <v>0.431</v>
       </c>
       <c r="L24" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M24" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="N24" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O24" t="n">
         <v>15.7</v>
@@ -4704,7 +4771,7 @@
         <v>22.6</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="R24" t="n">
         <v>9.5</v>
@@ -4716,10 +4783,10 @@
         <v>41.4</v>
       </c>
       <c r="U24" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V24" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W24" t="n">
         <v>8.199999999999999</v>
@@ -4731,19 +4798,19 @@
         <v>5.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA24" t="n">
         <v>19.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>-10</v>
+        <v>-10.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4755,13 +4822,13 @@
         <v>30</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>28</v>
       </c>
       <c r="AJ24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP24" t="n">
         <v>19</v>
@@ -4785,10 +4852,10 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT24" t="n">
         <v>30</v>
@@ -4812,7 +4879,7 @@
         <v>25</v>
       </c>
       <c r="BA24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" t="n">
         <v>22</v>
       </c>
       <c r="F25" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G25" t="n">
-        <v>0.278</v>
+        <v>0.275</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
@@ -4877,25 +4944,25 @@
         <v>25.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O25" t="n">
         <v>17.5</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R25" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="S25" t="n">
         <v>33.2</v>
       </c>
       <c r="T25" t="n">
-        <v>44.5</v>
+        <v>44.6</v>
       </c>
       <c r="U25" t="n">
         <v>20.7</v>
@@ -4913,19 +4980,19 @@
         <v>5.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA25" t="n">
         <v>21.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>100.8</v>
+        <v>100.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.8</v>
+        <v>-6.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
@@ -4961,16 +5028,16 @@
         <v>14</v>
       </c>
       <c r="AP25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR25" t="n">
         <v>6</v>
       </c>
       <c r="AS25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>7</v>
@@ -4982,13 +5049,13 @@
         <v>30</v>
       </c>
       <c r="AW25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY25" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ25" t="n">
         <v>30</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
       </c>
       <c r="G26" t="n">
-        <v>0.525</v>
+        <v>0.531</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5050,7 +5117,7 @@
         <v>85.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L26" t="n">
         <v>10.5</v>
@@ -5065,19 +5132,19 @@
         <v>17.4</v>
       </c>
       <c r="P26" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.752</v>
+        <v>0.753</v>
       </c>
       <c r="R26" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S26" t="n">
-        <v>33.8</v>
+        <v>34</v>
       </c>
       <c r="T26" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U26" t="n">
         <v>21.3</v>
@@ -5101,22 +5168,22 @@
         <v>19.5</v>
       </c>
       <c r="AB26" t="n">
-        <v>105</v>
+        <v>105.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
       </c>
       <c r="AE26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -5128,13 +5195,13 @@
         <v>9</v>
       </c>
       <c r="AK26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
       </c>
       <c r="AM26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN26" t="n">
         <v>3</v>
@@ -5146,13 +5213,13 @@
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>5</v>
@@ -5161,7 +5228,7 @@
         <v>21</v>
       </c>
       <c r="AV26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW26" t="n">
         <v>26</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E27" t="n">
         <v>32</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G27" t="n">
-        <v>0.405</v>
+        <v>0.4</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,7 +5296,7 @@
         <v>40.1</v>
       </c>
       <c r="J27" t="n">
-        <v>86.2</v>
+        <v>86.3</v>
       </c>
       <c r="K27" t="n">
         <v>0.465</v>
@@ -5241,16 +5308,16 @@
         <v>22.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O27" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P27" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.729</v>
+        <v>0.728</v>
       </c>
       <c r="R27" t="n">
         <v>10.6</v>
@@ -5277,28 +5344,28 @@
         <v>5.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA27" t="n">
         <v>22</v>
       </c>
       <c r="AB27" t="n">
-        <v>107</v>
+        <v>106.9</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>18</v>
@@ -5307,7 +5374,7 @@
         <v>4</v>
       </c>
       <c r="AJ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK27" t="n">
         <v>6</v>
@@ -5319,7 +5386,7 @@
         <v>21</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
@@ -5337,7 +5404,7 @@
         <v>14</v>
       </c>
       <c r="AT27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU27" t="n">
         <v>4</v>
@@ -5352,13 +5419,13 @@
         <v>20</v>
       </c>
       <c r="AY27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>15</v>
       </c>
       <c r="BA27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB27" t="n">
         <v>3</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -5408,40 +5475,40 @@
         <v>48</v>
       </c>
       <c r="I28" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="J28" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="L28" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="M28" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O28" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P28" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.804</v>
       </c>
       <c r="R28" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>34.6</v>
       </c>
       <c r="T28" t="n">
-        <v>44.1</v>
+        <v>43.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.7</v>
@@ -5456,7 +5523,7 @@
         <v>5.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z28" t="n">
         <v>17.4</v>
@@ -5465,13 +5532,13 @@
         <v>19.4</v>
       </c>
       <c r="AB28" t="n">
-        <v>103.6</v>
+        <v>103.9</v>
       </c>
       <c r="AC28" t="n">
         <v>11</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5510,7 +5577,7 @@
         <v>28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
         <v>25</v>
@@ -5519,19 +5586,19 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU28" t="n">
         <v>3</v>
       </c>
       <c r="AV28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
         <v>12</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
         <v>2</v>
@@ -5543,7 +5610,7 @@
         <v>23</v>
       </c>
       <c r="BB28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -5593,7 +5660,7 @@
         <v>36.5</v>
       </c>
       <c r="J29" t="n">
-        <v>81</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.45</v>
@@ -5605,13 +5672,13 @@
         <v>23.2</v>
       </c>
       <c r="N29" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O29" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="P29" t="n">
-        <v>26.8</v>
+        <v>27.1</v>
       </c>
       <c r="Q29" t="n">
         <v>0.78</v>
@@ -5620,22 +5687,22 @@
         <v>10.1</v>
       </c>
       <c r="S29" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T29" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U29" t="n">
         <v>18.6</v>
       </c>
       <c r="V29" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X29" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y29" t="n">
         <v>5.4</v>
@@ -5644,28 +5711,28 @@
         <v>19.7</v>
       </c>
       <c r="AA29" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>102.4</v>
+        <v>102.6</v>
       </c>
       <c r="AC29" t="n">
         <v>4.2</v>
       </c>
       <c r="AD29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE29" t="n">
         <v>5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>4</v>
       </c>
       <c r="AF29" t="n">
         <v>4</v>
       </c>
       <c r="AG29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH29" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI29" t="n">
         <v>27</v>
@@ -5674,7 +5741,7 @@
         <v>29</v>
       </c>
       <c r="AK29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>14</v>
@@ -5689,13 +5756,13 @@
         <v>2</v>
       </c>
       <c r="AP29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ29" t="n">
         <v>11</v>
       </c>
       <c r="AR29" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>21</v>
@@ -5707,7 +5774,7 @@
         <v>29</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW29" t="n">
         <v>15</v>
@@ -5719,16 +5786,16 @@
         <v>20</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB29" t="n">
         <v>14</v>
       </c>
       <c r="BC29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -5760,34 +5827,34 @@
         <v>79</v>
       </c>
       <c r="E30" t="n">
+        <v>39</v>
+      </c>
+      <c r="F30" t="n">
         <v>40</v>
       </c>
-      <c r="F30" t="n">
-        <v>39</v>
-      </c>
       <c r="G30" t="n">
-        <v>0.506</v>
+        <v>0.494</v>
       </c>
       <c r="H30" t="n">
         <v>48.7</v>
       </c>
       <c r="I30" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J30" t="n">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.448</v>
       </c>
       <c r="L30" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M30" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O30" t="n">
         <v>17.3</v>
@@ -5799,16 +5866,16 @@
         <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
         <v>32.5</v>
       </c>
       <c r="T30" t="n">
-        <v>43.4</v>
+        <v>43.3</v>
       </c>
       <c r="U30" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V30" t="n">
         <v>15</v>
@@ -5817,34 +5884,34 @@
         <v>7.7</v>
       </c>
       <c r="X30" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AA30" t="n">
         <v>20</v>
       </c>
       <c r="AB30" t="n">
-        <v>97.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>2</v>
@@ -5856,22 +5923,22 @@
         <v>30</v>
       </c>
       <c r="AK30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AN30" t="n">
         <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AQ30" t="n">
         <v>22</v>
@@ -5883,7 +5950,7 @@
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU30" t="n">
         <v>28</v>
@@ -5892,7 +5959,7 @@
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX30" t="n">
         <v>13</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
@@ -5954,22 +6021,22 @@
         <v>48.2</v>
       </c>
       <c r="I31" t="n">
-        <v>39.5</v>
+        <v>39.3</v>
       </c>
       <c r="J31" t="n">
-        <v>85.7</v>
+        <v>85.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L31" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="M31" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.36</v>
+        <v>0.357</v>
       </c>
       <c r="O31" t="n">
         <v>16.4</v>
@@ -5978,19 +6045,19 @@
         <v>22.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S31" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
         <v>41.6</v>
       </c>
       <c r="U31" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="V31" t="n">
         <v>14.4</v>
@@ -5999,34 +6066,34 @@
         <v>8.6</v>
       </c>
       <c r="X31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Y31" t="n">
         <v>4.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>104</v>
+        <v>103.7</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.8</v>
+        <v>-1</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>18</v>
       </c>
       <c r="AF31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH31" t="n">
         <v>26</v>
@@ -6047,10 +6114,10 @@
         <v>14</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP31" t="n">
         <v>20</v>
@@ -6059,13 +6126,13 @@
         <v>25</v>
       </c>
       <c r="AR31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS31" t="n">
         <v>22</v>
       </c>
       <c r="AT31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU31" t="n">
         <v>5</v>
@@ -6074,22 +6141,22 @@
         <v>16</v>
       </c>
       <c r="AW31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY31" t="n">
         <v>6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA31" t="n">
         <v>16</v>
       </c>
       <c r="BB31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-10-2015-16</t>
+          <t>2016-04-10</t>
         </is>
       </c>
     </row>
